--- a/output/topology_excel/3225.xlsx
+++ b/output/topology_excel/3225.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="n">
         <v>5</v>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
         <v>9</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" t="n">
         <v>19</v>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>346</v>
+        <v>445</v>
       </c>
       <c r="F21" t="n">
         <v>16</v>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>445</v>
+        <v>222</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="F23" t="n">
-        <v>154</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>144</v>
+        <v>223</v>
       </c>
       <c r="F24" t="n">
-        <v>109</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>345</v>
+        <v>60</v>
       </c>
       <c r="F26" t="n">
         <v>16</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>464</v>
+        <v>291</v>
       </c>
       <c r="F27" t="n">
         <v>16</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B28" t="n">
         <v>6</v>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>268</v>
+        <v>464</v>
       </c>
       <c r="F28" t="n">
-        <v>211</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>230</v>
+        <v>268</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,15 +1092,15 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>144</v>
       </c>
       <c r="F30" t="n">
-        <v>190</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B31" t="n">
         <v>11</v>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="F31" t="n">
-        <v>156</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B32" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="F32" t="n">
-        <v>153</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B33" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>324</v>
+        <v>72</v>
       </c>
       <c r="F33" t="n">
-        <v>240</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B34" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,19 +1180,19 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>457</v>
+        <v>303</v>
       </c>
       <c r="F34" t="n">
-        <v>308</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" t="n">
         <v>5</v>
       </c>
-      <c r="B35" t="n">
-        <v>21</v>
-      </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="F35" t="n">
         <v>16</v>
@@ -1213,7 +1213,7 @@
         <v>5</v>
       </c>
       <c r="B36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>230</v>
+        <v>144</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37">
@@ -1235,7 +1235,7 @@
         <v>5</v>
       </c>
       <c r="B37" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="F37" t="n">
         <v>16</v>
@@ -1257,7 +1257,7 @@
         <v>6</v>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>144</v>
+        <v>345</v>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>182</v>
+        <v>457</v>
       </c>
       <c r="F39" t="n">
-        <v>178</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B40" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>265</v>
+        <v>380</v>
       </c>
       <c r="F40" t="n">
         <v>16</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B41" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,18 +1334,18 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>271</v>
+        <v>230</v>
       </c>
       <c r="F41" t="n">
-        <v>137</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B42" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,18 +1356,18 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>396</v>
+        <v>229</v>
       </c>
       <c r="F42" t="n">
-        <v>319</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B43" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>227</v>
+        <v>136</v>
       </c>
       <c r="F43" t="n">
-        <v>125</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>93</v>
+        <v>207</v>
       </c>
       <c r="F44" t="n">
         <v>16</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="F45" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B46" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="F46" t="n">
         <v>16</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B47" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>229</v>
+        <v>162</v>
       </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B48" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="F48" t="n">
         <v>16</v>
@@ -1499,7 +1499,7 @@
         <v>13</v>
       </c>
       <c r="B49" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="F49" t="n">
-        <v>20</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50">
@@ -1521,7 +1521,7 @@
         <v>13</v>
       </c>
       <c r="B50" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>166</v>
+        <v>313</v>
       </c>
       <c r="F50" t="n">
         <v>16</v>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B51" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,18 +1554,18 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="F51" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B52" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="F52" t="n">
         <v>16</v>
@@ -1584,10 +1584,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B53" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,18 +1598,18 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>265</v>
+        <v>201</v>
       </c>
       <c r="F53" t="n">
-        <v>33</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B54" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>445</v>
+        <v>224</v>
       </c>
       <c r="F54" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B55" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="F55" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
@@ -1653,7 +1653,7 @@
         <v>16</v>
       </c>
       <c r="B56" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,18 +1664,18 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="F56" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B57" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>204</v>
+        <v>445</v>
       </c>
       <c r="F57" t="n">
-        <v>160</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58">
@@ -1697,7 +1697,7 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,15 +1708,15 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="F58" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B59" t="n">
         <v>19</v>
@@ -1730,18 +1730,18 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>218</v>
+        <v>306</v>
       </c>
       <c r="F59" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,18 +1752,18 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="F60" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B61" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="F61" t="n">
         <v>16</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B62" t="n">
         <v>25</v>
@@ -1796,32 +1796,252 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="F62" t="n">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
+        <v>19</v>
+      </c>
+      <c r="B63" t="n">
+        <v>20</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>227</v>
+      </c>
+      <c r="F63" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>20</v>
+      </c>
+      <c r="B64" t="n">
+        <v>25</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>199</v>
+      </c>
+      <c r="F64" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>21</v>
+      </c>
+      <c r="B65" t="n">
         <v>22</v>
       </c>
-      <c r="B63" t="n">
-        <v>25</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="n">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>93</v>
+      </c>
+      <c r="F65" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>22</v>
+      </c>
+      <c r="B66" t="n">
+        <v>23</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>80</v>
+      </c>
+      <c r="F66" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>22</v>
+      </c>
+      <c r="B67" t="n">
+        <v>24</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>40</v>
+      </c>
+      <c r="F67" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>23</v>
+      </c>
+      <c r="B68" t="n">
+        <v>24</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>131</v>
+      </c>
+      <c r="F68" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>24</v>
+      </c>
+      <c r="B69" t="n">
+        <v>26</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>230</v>
+      </c>
+      <c r="F69" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>26</v>
+      </c>
+      <c r="B70" t="n">
+        <v>28</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
         <v>201</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F70" t="n">
         <v>62</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="n">
+        <v>24</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>275</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" t="n">
+        <v>14</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>598</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2</v>
+      </c>
+      <c r="B73" t="n">
+        <v>20</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>152</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/3225.xlsx
+++ b/output/topology_excel/3225.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
         </is>
       </c>
     </row>
@@ -481,6 +501,10 @@
       <c r="F2" t="n">
         <v>16</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +527,10 @@
       <c r="F3" t="n">
         <v>16</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +553,10 @@
       <c r="F4" t="n">
         <v>68</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +579,10 @@
       <c r="F5" t="n">
         <v>16</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +605,10 @@
       <c r="F6" t="n">
         <v>20</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +631,10 @@
       <c r="F7" t="n">
         <v>16</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +657,10 @@
       <c r="F8" t="n">
         <v>16</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +683,10 @@
       <c r="F9" t="n">
         <v>16</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +709,10 @@
       <c r="F10" t="n">
         <v>16</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +735,10 @@
       <c r="F11" t="n">
         <v>16</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +761,10 @@
       <c r="F12" t="n">
         <v>22</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +787,10 @@
       <c r="F13" t="n">
         <v>22</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +813,10 @@
       <c r="F14" t="n">
         <v>16</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +839,10 @@
       <c r="F15" t="n">
         <v>16</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +865,10 @@
       <c r="F16" t="n">
         <v>16</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +891,10 @@
       <c r="F17" t="n">
         <v>16</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +917,10 @@
       <c r="F18" t="n">
         <v>33</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +943,10 @@
       <c r="F19" t="n">
         <v>16</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +969,10 @@
       <c r="F20" t="n">
         <v>51</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +995,10 @@
       <c r="F21" t="n">
         <v>16</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -919,8 +1019,12 @@
         <v>222</v>
       </c>
       <c r="F22" t="n">
-        <v>154</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1047,10 @@
       <c r="F23" t="n">
         <v>20</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -957,14 +1065,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="F24" t="n">
-        <v>156</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G24" t="n">
+        <v>136</v>
+      </c>
+      <c r="H24" t="n">
+        <v>16</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -979,14 +1095,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="F25" t="n">
-        <v>108</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G25" t="n">
+        <v>137</v>
+      </c>
+      <c r="H25" t="n">
+        <v>16</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1133,10 @@
       <c r="F26" t="n">
         <v>16</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1023,14 +1151,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>291</v>
+        <v>104</v>
       </c>
       <c r="F27" t="n">
         <v>16</v>
       </c>
+      <c r="G27" t="n">
+        <v>171</v>
+      </c>
+      <c r="H27" t="n">
+        <v>16</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1189,10 @@
       <c r="F28" t="n">
         <v>16</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1067,13 +1207,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>268</v>
+        <v>31</v>
       </c>
       <c r="F29" t="n">
-        <v>211</v>
+        <v>16</v>
+      </c>
+      <c r="G29" t="n">
+        <v>236</v>
+      </c>
+      <c r="H29" t="n">
+        <v>16</v>
+      </c>
+      <c r="I29" t="n">
+        <v>164</v>
+      </c>
+      <c r="J29" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -1097,6 +1249,10 @@
       <c r="F30" t="n">
         <v>20</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1111,14 +1267,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="F31" t="n">
-        <v>178</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G31" t="n">
+        <v>162</v>
+      </c>
+      <c r="H31" t="n">
+        <v>16</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1305,10 @@
       <c r="F32" t="n">
         <v>16</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1155,14 +1323,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G33" t="n">
+        <v>50</v>
+      </c>
+      <c r="H33" t="n">
+        <v>16</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1361,10 @@
       <c r="F34" t="n">
         <v>16</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1387,10 @@
       <c r="F35" t="n">
         <v>16</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1221,14 +1405,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="F36" t="n">
-        <v>109</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G36" t="n">
+        <v>128</v>
+      </c>
+      <c r="H36" t="n">
+        <v>16</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1443,10 @@
       <c r="F37" t="n">
         <v>16</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1469,10 @@
       <c r="F38" t="n">
         <v>16</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1287,14 +1487,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>457</v>
+        <v>292</v>
       </c>
       <c r="F39" t="n">
-        <v>308</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G39" t="n">
+        <v>441</v>
+      </c>
+      <c r="H39" t="n">
+        <v>16</v>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1525,10 @@
       <c r="F40" t="n">
         <v>16</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1551,10 @@
       <c r="F41" t="n">
         <v>16</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1577,10 @@
       <c r="F42" t="n">
         <v>16</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1603,10 @@
       <c r="F43" t="n">
         <v>16</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1629,10 @@
       <c r="F44" t="n">
         <v>16</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1655,10 @@
       <c r="F45" t="n">
         <v>20</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1681,10 @@
       <c r="F46" t="n">
         <v>16</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1707,10 @@
       <c r="F47" t="n">
         <v>33</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1733,10 @@
       <c r="F48" t="n">
         <v>16</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1513,8 +1757,12 @@
         <v>204</v>
       </c>
       <c r="F49" t="n">
-        <v>160</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1529,14 +1777,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>313</v>
+        <v>188</v>
       </c>
       <c r="F50" t="n">
         <v>16</v>
       </c>
+      <c r="G50" t="n">
+        <v>109</v>
+      </c>
+      <c r="H50" t="n">
+        <v>16</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1815,10 @@
       <c r="F51" t="n">
         <v>16</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1841,10 @@
       <c r="F52" t="n">
         <v>16</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1601,8 +1865,12 @@
         <v>201</v>
       </c>
       <c r="F53" t="n">
-        <v>166</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1893,10 @@
       <c r="F54" t="n">
         <v>16</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +1919,10 @@
       <c r="F55" t="n">
         <v>16</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +1945,10 @@
       <c r="F56" t="n">
         <v>33</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +1971,10 @@
       <c r="F57" t="n">
         <v>33</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +1997,10 @@
       <c r="F58" t="n">
         <v>22</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +2023,10 @@
       <c r="F59" t="n">
         <v>22</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +2049,10 @@
       <c r="F60" t="n">
         <v>17</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +2075,10 @@
       <c r="F61" t="n">
         <v>16</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1801,6 +2101,10 @@
       <c r="F62" t="n">
         <v>28</v>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1815,14 +2119,22 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>227</v>
+        <v>94</v>
       </c>
       <c r="F63" t="n">
-        <v>125</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G63" t="n">
+        <v>196</v>
+      </c>
+      <c r="H63" t="n">
+        <v>31</v>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1837,14 +2149,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="F64" t="n">
-        <v>137</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G64" t="n">
+        <v>121</v>
+      </c>
+      <c r="H64" t="n">
+        <v>16</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1867,6 +2187,10 @@
       <c r="F65" t="n">
         <v>16</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1889,6 +2213,10 @@
       <c r="F66" t="n">
         <v>16</v>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1911,6 +2239,10 @@
       <c r="F67" t="n">
         <v>16</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1925,14 +2257,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="F68" t="n">
-        <v>57</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G68" t="n">
+        <v>41</v>
+      </c>
+      <c r="H68" t="n">
+        <v>16</v>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1955,6 +2295,10 @@
       <c r="F69" t="n">
         <v>16</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1969,14 +2313,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>201</v>
+        <v>46</v>
       </c>
       <c r="F70" t="n">
-        <v>62</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G70" t="n">
+        <v>185</v>
+      </c>
+      <c r="H70" t="n">
+        <v>16</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1999,6 +2351,10 @@
       <c r="F71" t="n">
         <v>1</v>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2021,6 +2377,10 @@
       <c r="F72" t="n">
         <v>1</v>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2043,6 +2403,10 @@
       <c r="F73" t="n">
         <v>1</v>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
